--- a/artfynd/A 63059-2025 artfynd.xlsx
+++ b/artfynd/A 63059-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136294807</v>
       </c>
       <c r="B2" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136294782</v>
       </c>
       <c r="B3" t="n">
-        <v>92534</v>
+        <v>92537</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136295668</v>
       </c>
       <c r="B4" t="n">
-        <v>92776</v>
+        <v>92779</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136423298</v>
       </c>
       <c r="B5" t="n">
-        <v>92776</v>
+        <v>92779</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>136423296</v>
       </c>
       <c r="B6" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>136284253</v>
       </c>
       <c r="B13" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136284254</v>
       </c>
       <c r="B14" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>136284260</v>
       </c>
       <c r="B15" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>136284262</v>
       </c>
       <c r="B16" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>136284267</v>
       </c>
       <c r="B17" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>136284268</v>
       </c>
       <c r="B18" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>136284270</v>
       </c>
       <c r="B19" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>136284271</v>
       </c>
       <c r="B20" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>136284273</v>
       </c>
       <c r="B21" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>136284274</v>
       </c>
       <c r="B22" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>136295749</v>
       </c>
       <c r="B23" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>136295830</v>
       </c>
       <c r="B24" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>136295888</v>
       </c>
       <c r="B25" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>136296170</v>
       </c>
       <c r="B26" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>136296499</v>
       </c>
       <c r="B27" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>136423302</v>
       </c>
       <c r="B28" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>136423405</v>
       </c>
       <c r="B29" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>136423413</v>
       </c>
       <c r="B30" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>136423414</v>
       </c>
       <c r="B31" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>136423415</v>
       </c>
       <c r="B32" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>136423418</v>
       </c>
       <c r="B33" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>136423419</v>
       </c>
       <c r="B34" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         <v>136294881</v>
       </c>
       <c r="B35" t="n">
-        <v>106483</v>
+        <v>106486</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>136295698</v>
       </c>
       <c r="B36" t="n">
-        <v>106483</v>
+        <v>106486</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>136295567</v>
       </c>
       <c r="B37" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         <v>136423286</v>
       </c>
       <c r="B38" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>136423288</v>
       </c>
       <c r="B39" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v>136423295</v>
       </c>
       <c r="B40" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>136284256</v>
       </c>
       <c r="B41" t="n">
-        <v>99148</v>
+        <v>99151</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 63059-2025 artfynd.xlsx
+++ b/artfynd/A 63059-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136294807</v>
       </c>
       <c r="B2" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136294782</v>
       </c>
       <c r="B3" t="n">
-        <v>92537</v>
+        <v>92538</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136295668</v>
       </c>
       <c r="B4" t="n">
-        <v>92779</v>
+        <v>92780</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136423298</v>
       </c>
       <c r="B5" t="n">
-        <v>92779</v>
+        <v>92780</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>136423296</v>
       </c>
       <c r="B6" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>136284253</v>
       </c>
       <c r="B13" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136284254</v>
       </c>
       <c r="B14" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>136284260</v>
       </c>
       <c r="B15" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>136284262</v>
       </c>
       <c r="B16" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>136284267</v>
       </c>
       <c r="B17" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>136284268</v>
       </c>
       <c r="B18" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>136284270</v>
       </c>
       <c r="B19" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>136284271</v>
       </c>
       <c r="B20" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>136284273</v>
       </c>
       <c r="B21" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>136284274</v>
       </c>
       <c r="B22" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>136295749</v>
       </c>
       <c r="B23" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>136295830</v>
       </c>
       <c r="B24" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>136295888</v>
       </c>
       <c r="B25" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>136296170</v>
       </c>
       <c r="B26" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>136296499</v>
       </c>
       <c r="B27" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>136423302</v>
       </c>
       <c r="B28" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>136423405</v>
       </c>
       <c r="B29" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>136423413</v>
       </c>
       <c r="B30" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>136423414</v>
       </c>
       <c r="B31" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>136423415</v>
       </c>
       <c r="B32" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>136423418</v>
       </c>
       <c r="B33" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>136423419</v>
       </c>
       <c r="B34" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         <v>136294881</v>
       </c>
       <c r="B35" t="n">
-        <v>106486</v>
+        <v>106487</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>136295698</v>
       </c>
       <c r="B36" t="n">
-        <v>106486</v>
+        <v>106487</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>136295567</v>
       </c>
       <c r="B37" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         <v>136423286</v>
       </c>
       <c r="B38" t="n">
-        <v>101555</v>
+        <v>101556</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>136423288</v>
       </c>
       <c r="B39" t="n">
-        <v>101555</v>
+        <v>101556</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v>136423295</v>
       </c>
       <c r="B40" t="n">
-        <v>101555</v>
+        <v>101556</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>136284256</v>
       </c>
       <c r="B41" t="n">
-        <v>99151</v>
+        <v>99152</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 63059-2025 artfynd.xlsx
+++ b/artfynd/A 63059-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136294807</v>
       </c>
       <c r="B2" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136294782</v>
       </c>
       <c r="B3" t="n">
-        <v>92538</v>
+        <v>92543</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136295668</v>
       </c>
       <c r="B4" t="n">
-        <v>92780</v>
+        <v>92785</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136423298</v>
       </c>
       <c r="B5" t="n">
-        <v>92780</v>
+        <v>92785</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>136423296</v>
       </c>
       <c r="B6" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>136284272</v>
       </c>
       <c r="B7" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136284275</v>
       </c>
       <c r="B8" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>136423289</v>
       </c>
       <c r="B9" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>136423300</v>
       </c>
       <c r="B10" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>136284265</v>
       </c>
       <c r="B12" t="n">
-        <v>45294</v>
+        <v>45296</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>136284253</v>
       </c>
       <c r="B13" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136284254</v>
       </c>
       <c r="B14" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>136284260</v>
       </c>
       <c r="B15" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>136284262</v>
       </c>
       <c r="B16" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>136284267</v>
       </c>
       <c r="B17" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>136284268</v>
       </c>
       <c r="B18" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>136284270</v>
       </c>
       <c r="B19" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>136284271</v>
       </c>
       <c r="B20" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>136284273</v>
       </c>
       <c r="B21" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>136284274</v>
       </c>
       <c r="B22" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>136295749</v>
       </c>
       <c r="B23" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>136295830</v>
       </c>
       <c r="B24" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>136295888</v>
       </c>
       <c r="B25" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>136296170</v>
       </c>
       <c r="B26" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>136296499</v>
       </c>
       <c r="B27" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>136423302</v>
       </c>
       <c r="B28" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>136423405</v>
       </c>
       <c r="B29" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>136423413</v>
       </c>
       <c r="B30" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>136423414</v>
       </c>
       <c r="B31" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>136423415</v>
       </c>
       <c r="B32" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>136423418</v>
       </c>
       <c r="B33" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>136423419</v>
       </c>
       <c r="B34" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         <v>136294881</v>
       </c>
       <c r="B35" t="n">
-        <v>106487</v>
+        <v>106492</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>136295698</v>
       </c>
       <c r="B36" t="n">
-        <v>106487</v>
+        <v>106492</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>136295567</v>
       </c>
       <c r="B37" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         <v>136423286</v>
       </c>
       <c r="B38" t="n">
-        <v>101556</v>
+        <v>101561</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>136423288</v>
       </c>
       <c r="B39" t="n">
-        <v>101556</v>
+        <v>101561</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v>136423295</v>
       </c>
       <c r="B40" t="n">
-        <v>101556</v>
+        <v>101561</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>136284256</v>
       </c>
       <c r="B41" t="n">
-        <v>99152</v>
+        <v>99157</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 63059-2025 artfynd.xlsx
+++ b/artfynd/A 63059-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136294807</v>
       </c>
       <c r="B2" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136294782</v>
       </c>
       <c r="B3" t="n">
-        <v>92543</v>
+        <v>92545</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136295668</v>
       </c>
       <c r="B4" t="n">
-        <v>92785</v>
+        <v>92787</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136423298</v>
       </c>
       <c r="B5" t="n">
-        <v>92785</v>
+        <v>92787</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>136423296</v>
       </c>
       <c r="B6" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>136284253</v>
       </c>
       <c r="B13" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136284254</v>
       </c>
       <c r="B14" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>136284260</v>
       </c>
       <c r="B15" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>136284262</v>
       </c>
       <c r="B16" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>136284267</v>
       </c>
       <c r="B17" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>136284268</v>
       </c>
       <c r="B18" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>136284270</v>
       </c>
       <c r="B19" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>136284271</v>
       </c>
       <c r="B20" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>136284273</v>
       </c>
       <c r="B21" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>136284274</v>
       </c>
       <c r="B22" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>136295749</v>
       </c>
       <c r="B23" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>136295830</v>
       </c>
       <c r="B24" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>136295888</v>
       </c>
       <c r="B25" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>136296170</v>
       </c>
       <c r="B26" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>136296499</v>
       </c>
       <c r="B27" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>136423302</v>
       </c>
       <c r="B28" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>136423405</v>
       </c>
       <c r="B29" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>136423413</v>
       </c>
       <c r="B30" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>136423414</v>
       </c>
       <c r="B31" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>136423415</v>
       </c>
       <c r="B32" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>136423418</v>
       </c>
       <c r="B33" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>136423419</v>
       </c>
       <c r="B34" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         <v>136294881</v>
       </c>
       <c r="B35" t="n">
-        <v>106492</v>
+        <v>106494</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>136295698</v>
       </c>
       <c r="B36" t="n">
-        <v>106492</v>
+        <v>106494</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>136295567</v>
       </c>
       <c r="B37" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         <v>136423286</v>
       </c>
       <c r="B38" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>136423288</v>
       </c>
       <c r="B39" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v>136423295</v>
       </c>
       <c r="B40" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>136284256</v>
       </c>
       <c r="B41" t="n">
-        <v>99157</v>
+        <v>99159</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 63059-2025 artfynd.xlsx
+++ b/artfynd/A 63059-2025 artfynd.xlsx
@@ -1013,7 +1013,7 @@
         <v>136423298</v>
       </c>
       <c r="B5" t="n">
-        <v>92787</v>
+        <v>92789</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>136423296</v>
       </c>
       <c r="B6" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>136423302</v>
       </c>
       <c r="B28" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>136423405</v>
       </c>
       <c r="B29" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>136423413</v>
       </c>
       <c r="B30" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>136423414</v>
       </c>
       <c r="B31" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>136423415</v>
       </c>
       <c r="B32" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>136423418</v>
       </c>
       <c r="B33" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>136423419</v>
       </c>
       <c r="B34" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         <v>136423286</v>
       </c>
       <c r="B38" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>136423288</v>
       </c>
       <c r="B39" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v>136423295</v>
       </c>
       <c r="B40" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 63059-2025 artfynd.xlsx
+++ b/artfynd/A 63059-2025 artfynd.xlsx
@@ -1013,7 +1013,7 @@
         <v>136423298</v>
       </c>
       <c r="B5" t="n">
-        <v>92789</v>
+        <v>92791</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>136423296</v>
       </c>
       <c r="B6" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>136423302</v>
       </c>
       <c r="B28" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>136423405</v>
       </c>
       <c r="B29" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>136423413</v>
       </c>
       <c r="B30" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>136423414</v>
       </c>
       <c r="B31" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>136423415</v>
       </c>
       <c r="B32" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>136423418</v>
       </c>
       <c r="B33" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>136423419</v>
       </c>
       <c r="B34" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         <v>136423286</v>
       </c>
       <c r="B38" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>136423288</v>
       </c>
       <c r="B39" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v>136423295</v>
       </c>
       <c r="B40" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 63059-2025 artfynd.xlsx
+++ b/artfynd/A 63059-2025 artfynd.xlsx
@@ -1013,7 +1013,7 @@
         <v>136423298</v>
       </c>
       <c r="B5" t="n">
-        <v>92791</v>
+        <v>92792</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>136423296</v>
       </c>
       <c r="B6" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>136423302</v>
       </c>
       <c r="B28" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>136423405</v>
       </c>
       <c r="B29" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>136423413</v>
       </c>
       <c r="B30" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>136423414</v>
       </c>
       <c r="B31" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>136423415</v>
       </c>
       <c r="B32" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>136423418</v>
       </c>
       <c r="B33" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>136423419</v>
       </c>
       <c r="B34" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         <v>136423286</v>
       </c>
       <c r="B38" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>136423288</v>
       </c>
       <c r="B39" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v>136423295</v>
       </c>
       <c r="B40" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
